--- a/APIテスト仕様書(facilities).xlsx
+++ b/APIテスト仕様書(facilities).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr codeName="ThisWorkbook" checkCompatibility="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tie187090\Box\124_都市機構／維持保全BIM（パートナー含む）\2025年度\02_VRビューワ\テスト\APIテスト\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tistgu4s.sharepoint.com/sites/TISI__VR/Shared Documents/開発/02_VRビューワ/テスト/APIテスト/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98328E06-A797-45A3-897C-A43BC77C8240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2998EFD5-764B-4870-8497-FD110B2512E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="885" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -641,7 +641,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="331">
   <si>
     <t>PJ名</t>
   </si>
@@ -4445,6 +4445,27 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>ガッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細取得
+GET /facilities/{facilityid}（前のfacilityidとは別の施設）
+（USER01）</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>シセツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5941,11 +5962,14 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5953,8 +5977,23 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6000,24 +6039,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -8203,23 +8224,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
+      <c r="B1" s="67"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2"/>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="64" t="s">
+      <c r="F1" s="69"/>
+      <c r="G1" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="61"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="67"/>
       <c r="J1" s="3"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -8228,31 +8249,31 @@
       <c r="O1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="64" t="s">
+      <c r="P1" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="55">
+      <c r="Q1" s="67"/>
+      <c r="R1" s="64">
         <v>46153</v>
       </c>
-      <c r="S1" s="56"/>
+      <c r="S1" s="65"/>
     </row>
     <row r="2" spans="1:19" ht="16.5">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="61"/>
+      <c r="B2" s="67"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="72"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="78"/>
       <c r="J2" s="9"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
@@ -8261,27 +8282,27 @@
       <c r="O2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="55" t="s">
+      <c r="P2" s="70"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="56"/>
+      <c r="S2" s="65"/>
     </row>
     <row r="3" spans="1:19" ht="16.5">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="61"/>
+      <c r="B3" s="67"/>
       <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="80"/>
       <c r="J3" s="13"/>
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
@@ -8290,12 +8311,12 @@
       <c r="O3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="55" t="s">
+      <c r="P3" s="70"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="56"/>
+      <c r="S3" s="65"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="17" t="s">
@@ -8359,18 +8380,18 @@
       <c r="A6" s="30">
         <v>1</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="58"/>
+      <c r="C6" s="59"/>
       <c r="D6" s="30">
         <v>1</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="58"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="59"/>
       <c r="H6" s="30">
         <v>1</v>
       </c>
@@ -8392,12 +8413,12 @@
     </row>
     <row r="7" spans="1:19" ht="126">
       <c r="A7" s="30"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="30"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="30">
         <v>2</v>
       </c>
@@ -8422,9 +8443,9 @@
       <c r="B8" s="48"/>
       <c r="C8" s="49"/>
       <c r="D8" s="30"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="61"/>
       <c r="H8" s="30">
         <v>3</v>
       </c>
@@ -8586,11 +8607,11 @@
       <c r="D14" s="30">
         <v>2</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="E14" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="58"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="59"/>
       <c r="H14" s="30">
         <v>1</v>
       </c>
@@ -8615,9 +8636,9 @@
       <c r="B15" s="48"/>
       <c r="C15" s="49"/>
       <c r="D15" s="30"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="59"/>
       <c r="H15" s="30">
         <v>2</v>
       </c>
@@ -8938,18 +8959,18 @@
       <c r="A27" s="30">
         <v>2</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="58"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="30">
         <v>1</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E27" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="59"/>
-      <c r="G27" s="58"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="59"/>
       <c r="H27" s="30">
         <v>1</v>
       </c>
@@ -8974,9 +8995,9 @@
       <c r="B28" s="48"/>
       <c r="C28" s="49"/>
       <c r="D28" s="30"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="59"/>
       <c r="H28" s="30">
         <v>2</v>
       </c>
@@ -9297,18 +9318,18 @@
       <c r="A40" s="30">
         <v>3</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="58"/>
+      <c r="C40" s="59"/>
       <c r="D40" s="30">
         <v>1</v>
       </c>
-      <c r="E40" s="57" t="s">
+      <c r="E40" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F40" s="59"/>
-      <c r="G40" s="58"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="59"/>
       <c r="H40" s="30">
         <v>1</v>
       </c>
@@ -9333,9 +9354,9 @@
       <c r="B41" s="48"/>
       <c r="C41" s="49"/>
       <c r="D41" s="30"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="59"/>
       <c r="H41" s="30">
         <v>2</v>
       </c>
@@ -9656,18 +9677,18 @@
       <c r="A53" s="30">
         <v>4</v>
       </c>
-      <c r="B53" s="57" t="s">
+      <c r="B53" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="C53" s="58"/>
+      <c r="C53" s="59"/>
       <c r="D53" s="30">
         <v>1</v>
       </c>
-      <c r="E53" s="57" t="s">
+      <c r="E53" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F53" s="59"/>
-      <c r="G53" s="58"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="59"/>
       <c r="H53" s="30">
         <v>1</v>
       </c>
@@ -9691,18 +9712,18 @@
       <c r="A54" s="30">
         <v>5</v>
       </c>
-      <c r="B54" s="57" t="s">
+      <c r="B54" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="C54" s="58"/>
+      <c r="C54" s="59"/>
       <c r="D54" s="30">
         <v>1</v>
       </c>
-      <c r="E54" s="57" t="s">
+      <c r="E54" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F54" s="59"/>
-      <c r="G54" s="58"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="59"/>
       <c r="H54" s="30">
         <v>1</v>
       </c>
@@ -9724,12 +9745,12 @@
     </row>
     <row r="55" spans="1:19" ht="126">
       <c r="A55" s="30"/>
-      <c r="B55" s="57"/>
-      <c r="C55" s="58"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="59"/>
       <c r="D55" s="30"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="59"/>
-      <c r="G55" s="58"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="59"/>
       <c r="H55" s="30">
         <v>2</v>
       </c>
@@ -9754,9 +9775,9 @@
       <c r="B56" s="48"/>
       <c r="C56" s="49"/>
       <c r="D56" s="30"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="77"/>
+      <c r="E56" s="60"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="61"/>
       <c r="H56" s="30">
         <v>3</v>
       </c>
@@ -9918,11 +9939,11 @@
       <c r="D62" s="30">
         <v>2</v>
       </c>
-      <c r="E62" s="57" t="s">
+      <c r="E62" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F62" s="59"/>
-      <c r="G62" s="58"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="59"/>
       <c r="H62" s="30">
         <v>1</v>
       </c>
@@ -9947,9 +9968,9 @@
       <c r="B63" s="48"/>
       <c r="C63" s="49"/>
       <c r="D63" s="30"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="63"/>
+      <c r="G63" s="59"/>
       <c r="H63" s="30">
         <v>2</v>
       </c>
@@ -10270,18 +10291,18 @@
       <c r="A75" s="30">
         <v>6</v>
       </c>
-      <c r="B75" s="57" t="s">
+      <c r="B75" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="C75" s="58"/>
+      <c r="C75" s="59"/>
       <c r="D75" s="30">
         <v>1</v>
       </c>
-      <c r="E75" s="57" t="s">
+      <c r="E75" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F75" s="59"/>
-      <c r="G75" s="58"/>
+      <c r="F75" s="63"/>
+      <c r="G75" s="59"/>
       <c r="H75" s="30">
         <v>1</v>
       </c>
@@ -10306,9 +10327,9 @@
       <c r="B76" s="48"/>
       <c r="C76" s="49"/>
       <c r="D76" s="30"/>
-      <c r="E76" s="57"/>
-      <c r="F76" s="59"/>
-      <c r="G76" s="58"/>
+      <c r="E76" s="58"/>
+      <c r="F76" s="63"/>
+      <c r="G76" s="59"/>
       <c r="H76" s="30">
         <v>2</v>
       </c>
@@ -10629,18 +10650,18 @@
       <c r="A88" s="30">
         <v>7</v>
       </c>
-      <c r="B88" s="57" t="s">
+      <c r="B88" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="C88" s="58"/>
+      <c r="C88" s="59"/>
       <c r="D88" s="30">
         <v>1</v>
       </c>
-      <c r="E88" s="57" t="s">
+      <c r="E88" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F88" s="59"/>
-      <c r="G88" s="58"/>
+      <c r="F88" s="63"/>
+      <c r="G88" s="59"/>
       <c r="H88" s="30">
         <v>1</v>
       </c>
@@ -10665,9 +10686,9 @@
       <c r="B89" s="48"/>
       <c r="C89" s="49"/>
       <c r="D89" s="30"/>
-      <c r="E89" s="57"/>
-      <c r="F89" s="59"/>
-      <c r="G89" s="58"/>
+      <c r="E89" s="58"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="59"/>
       <c r="H89" s="30">
         <v>2</v>
       </c>
@@ -10988,18 +11009,18 @@
       <c r="A101" s="30">
         <v>8</v>
       </c>
-      <c r="B101" s="57" t="s">
+      <c r="B101" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="58"/>
+      <c r="C101" s="59"/>
       <c r="D101" s="30">
         <v>1</v>
       </c>
-      <c r="E101" s="57" t="s">
+      <c r="E101" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F101" s="59"/>
-      <c r="G101" s="58"/>
+      <c r="F101" s="63"/>
+      <c r="G101" s="59"/>
       <c r="H101" s="30">
         <v>1</v>
       </c>
@@ -11042,12 +11063,12 @@
     </row>
     <row r="103" spans="1:19" ht="31.5" customHeight="1">
       <c r="A103" s="38"/>
-      <c r="B103" s="78"/>
-      <c r="C103" s="79"/>
+      <c r="B103" s="55"/>
+      <c r="C103" s="56"/>
       <c r="D103" s="38"/>
-      <c r="E103" s="78"/>
-      <c r="F103" s="80"/>
-      <c r="G103" s="79"/>
+      <c r="E103" s="55"/>
+      <c r="F103" s="57"/>
+      <c r="G103" s="56"/>
       <c r="H103" s="38"/>
       <c r="I103" s="46"/>
       <c r="J103" s="39"/>
@@ -11094,13 +11115,29 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="E101:G101"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:G75"/>
-    <mergeCell ref="E76:G76"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="E40:G40"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:I1"/>
@@ -11117,29 +11154,13 @@
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="E27:G27"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="E101:G101"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="E88:G88"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
@@ -11190,23 +11211,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
+      <c r="B1" s="67"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2"/>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="64" t="s">
+      <c r="F1" s="69"/>
+      <c r="G1" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="61"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="67"/>
       <c r="J1" s="3"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -11215,31 +11236,31 @@
       <c r="O1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="64" t="s">
+      <c r="P1" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="55">
+      <c r="Q1" s="67"/>
+      <c r="R1" s="64">
         <v>46153</v>
       </c>
-      <c r="S1" s="56"/>
+      <c r="S1" s="65"/>
     </row>
     <row r="2" spans="1:19" ht="16.5">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="61"/>
+      <c r="B2" s="67"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="72"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="78"/>
       <c r="J2" s="9"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
@@ -11248,27 +11269,27 @@
       <c r="O2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="55" t="s">
+      <c r="P2" s="70"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="56"/>
+      <c r="S2" s="65"/>
     </row>
     <row r="3" spans="1:19" ht="16.5">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="61"/>
+      <c r="B3" s="67"/>
       <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="80"/>
       <c r="J3" s="13"/>
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
@@ -11277,12 +11298,12 @@
       <c r="O3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="55" t="s">
+      <c r="P3" s="70"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="56"/>
+      <c r="S3" s="65"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="17" t="s">
@@ -11346,18 +11367,18 @@
       <c r="A6" s="30">
         <v>1</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="58"/>
+      <c r="C6" s="59"/>
       <c r="D6" s="30">
         <v>1</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="58"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="59"/>
       <c r="H6" s="30">
         <v>1</v>
       </c>
@@ -11379,12 +11400,12 @@
     </row>
     <row r="7" spans="1:19" ht="126">
       <c r="A7" s="30"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="30"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="30">
         <v>2</v>
       </c>
@@ -11409,9 +11430,9 @@
       <c r="B8" s="48"/>
       <c r="C8" s="49"/>
       <c r="D8" s="30"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="61"/>
       <c r="H8" s="30">
         <v>3</v>
       </c>
@@ -11546,11 +11567,11 @@
       <c r="D13" s="30">
         <v>2</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="58"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="59"/>
       <c r="H13" s="30">
         <v>1</v>
       </c>
@@ -11575,9 +11596,9 @@
       <c r="B14" s="48"/>
       <c r="C14" s="49"/>
       <c r="D14" s="30"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="59"/>
       <c r="H14" s="30">
         <v>2</v>
       </c>
@@ -11898,18 +11919,18 @@
       <c r="A26" s="30">
         <v>2</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="58"/>
+      <c r="C26" s="59"/>
       <c r="D26" s="30">
         <v>1</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="59"/>
-      <c r="G26" s="58"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="59"/>
       <c r="H26" s="30">
         <v>1</v>
       </c>
@@ -11934,9 +11955,9 @@
       <c r="B27" s="48"/>
       <c r="C27" s="49"/>
       <c r="D27" s="30"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="59"/>
       <c r="H27" s="30">
         <v>2</v>
       </c>
@@ -12255,20 +12276,20 @@
     </row>
     <row r="39" spans="1:19" ht="136.5" customHeight="1">
       <c r="A39" s="30">
-        <v>2</v>
-      </c>
-      <c r="B39" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="C39" s="58"/>
+      <c r="C39" s="59"/>
       <c r="D39" s="30">
         <v>1</v>
       </c>
-      <c r="E39" s="57" t="s">
+      <c r="E39" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="59"/>
-      <c r="G39" s="58"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="59"/>
       <c r="H39" s="30">
         <v>1</v>
       </c>
@@ -12290,20 +12311,20 @@
     </row>
     <row r="40" spans="1:19" ht="126">
       <c r="A40" s="30">
-        <v>5</v>
-      </c>
-      <c r="B40" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="C40" s="58"/>
+      <c r="C40" s="59"/>
       <c r="D40" s="30">
         <v>1</v>
       </c>
-      <c r="E40" s="57" t="s">
+      <c r="E40" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F40" s="59"/>
-      <c r="G40" s="58"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="59"/>
       <c r="H40" s="30">
         <v>1</v>
       </c>
@@ -12325,12 +12346,12 @@
     </row>
     <row r="41" spans="1:19" ht="126">
       <c r="A41" s="30"/>
-      <c r="B41" s="57"/>
-      <c r="C41" s="58"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="59"/>
       <c r="D41" s="30"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="59"/>
       <c r="H41" s="30">
         <v>2</v>
       </c>
@@ -12355,9 +12376,9 @@
       <c r="B42" s="48"/>
       <c r="C42" s="49"/>
       <c r="D42" s="30"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="77"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="61"/>
       <c r="H42" s="30">
         <v>3</v>
       </c>
@@ -12492,11 +12513,11 @@
       <c r="D47" s="30">
         <v>2</v>
       </c>
-      <c r="E47" s="57" t="s">
+      <c r="E47" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F47" s="59"/>
-      <c r="G47" s="58"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="59"/>
       <c r="H47" s="30">
         <v>1</v>
       </c>
@@ -12521,9 +12542,9 @@
       <c r="B48" s="48"/>
       <c r="C48" s="49"/>
       <c r="D48" s="30"/>
-      <c r="E48" s="57"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="58"/>
+      <c r="E48" s="58"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="59"/>
       <c r="H48" s="30">
         <v>2</v>
       </c>
@@ -12842,20 +12863,20 @@
     </row>
     <row r="60" spans="1:19" ht="117" customHeight="1">
       <c r="A60" s="30">
-        <v>6</v>
-      </c>
-      <c r="B60" s="57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="58"/>
+      <c r="C60" s="59"/>
       <c r="D60" s="30">
         <v>1</v>
       </c>
-      <c r="E60" s="57" t="s">
+      <c r="E60" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F60" s="59"/>
-      <c r="G60" s="58"/>
+      <c r="F60" s="63"/>
+      <c r="G60" s="59"/>
       <c r="H60" s="30">
         <v>1</v>
       </c>
@@ -12880,9 +12901,9 @@
       <c r="B61" s="48"/>
       <c r="C61" s="49"/>
       <c r="D61" s="30"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="58"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="59"/>
       <c r="H61" s="30">
         <v>2</v>
       </c>
@@ -13201,20 +13222,20 @@
     </row>
     <row r="73" spans="1:19" ht="129" customHeight="1">
       <c r="A73" s="30">
-        <v>2</v>
-      </c>
-      <c r="B73" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="C73" s="58"/>
+      <c r="C73" s="59"/>
       <c r="D73" s="30">
         <v>1</v>
       </c>
-      <c r="E73" s="57" t="s">
+      <c r="E73" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F73" s="59"/>
-      <c r="G73" s="58"/>
+      <c r="F73" s="63"/>
+      <c r="G73" s="59"/>
       <c r="H73" s="30">
         <v>1</v>
       </c>
@@ -13236,12 +13257,12 @@
     </row>
     <row r="74" spans="1:19" ht="31.5" customHeight="1">
       <c r="A74" s="38"/>
-      <c r="B74" s="78"/>
-      <c r="C74" s="79"/>
+      <c r="B74" s="55"/>
+      <c r="C74" s="56"/>
       <c r="D74" s="38"/>
-      <c r="E74" s="78"/>
-      <c r="F74" s="80"/>
-      <c r="G74" s="79"/>
+      <c r="E74" s="55"/>
+      <c r="F74" s="57"/>
+      <c r="G74" s="56"/>
       <c r="H74" s="38"/>
       <c r="I74" s="46"/>
       <c r="J74" s="39"/>
@@ -13288,30 +13309,6 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="E2:F3"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="B73:C73"/>
@@ -13328,6 +13325,30 @@
     <mergeCell ref="E47:G47"/>
     <mergeCell ref="E27:G27"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="E2:F3"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="E74:G74"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
@@ -13378,23 +13399,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
+      <c r="B1" s="67"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2"/>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="64" t="s">
+      <c r="F1" s="69"/>
+      <c r="G1" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="61"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="67"/>
       <c r="J1" s="3"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -13403,31 +13424,31 @@
       <c r="O1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="64" t="s">
+      <c r="P1" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="55">
+      <c r="Q1" s="67"/>
+      <c r="R1" s="64">
         <v>46153</v>
       </c>
-      <c r="S1" s="56"/>
+      <c r="S1" s="65"/>
     </row>
     <row r="2" spans="1:19" ht="16.5">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="61"/>
+      <c r="B2" s="67"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="72"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="78"/>
       <c r="J2" s="9"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
@@ -13436,27 +13457,27 @@
       <c r="O2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="55" t="s">
+      <c r="P2" s="70"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="56"/>
+      <c r="S2" s="65"/>
     </row>
     <row r="3" spans="1:19" ht="16.5">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="61"/>
+      <c r="B3" s="67"/>
       <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="80"/>
       <c r="J3" s="13"/>
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
@@ -13465,12 +13486,12 @@
       <c r="O3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="55" t="s">
+      <c r="P3" s="70"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="56"/>
+      <c r="S3" s="65"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="17" t="s">
@@ -13534,18 +13555,18 @@
       <c r="A6" s="30">
         <v>1</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="58"/>
+      <c r="C6" s="59"/>
       <c r="D6" s="30">
         <v>1</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="58"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="59"/>
       <c r="H6" s="30">
         <v>1</v>
       </c>
@@ -13567,12 +13588,12 @@
     </row>
     <row r="7" spans="1:19" ht="126">
       <c r="A7" s="30"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="30"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="30">
         <v>2</v>
       </c>
@@ -13597,9 +13618,9 @@
       <c r="B8" s="48"/>
       <c r="C8" s="49"/>
       <c r="D8" s="30"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="61"/>
       <c r="H8" s="30">
         <v>3</v>
       </c>
@@ -13761,11 +13782,11 @@
       <c r="D14" s="30">
         <v>2</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="E14" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="58"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="59"/>
       <c r="H14" s="30">
         <v>1</v>
       </c>
@@ -15003,11 +15024,11 @@
       <c r="D60" s="30">
         <v>3</v>
       </c>
-      <c r="E60" s="57" t="s">
+      <c r="E60" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="F60" s="59"/>
-      <c r="G60" s="58"/>
+      <c r="F60" s="63"/>
+      <c r="G60" s="59"/>
       <c r="H60" s="30"/>
       <c r="I60" s="51" t="s">
         <v>201</v>
@@ -15029,18 +15050,18 @@
       <c r="A61" s="30">
         <v>2</v>
       </c>
-      <c r="B61" s="57" t="s">
+      <c r="B61" s="58" t="s">
         <v>203</v>
       </c>
-      <c r="C61" s="58"/>
+      <c r="C61" s="59"/>
       <c r="D61" s="30">
         <v>1</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F61" s="59"/>
-      <c r="G61" s="58"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="59"/>
       <c r="H61" s="30">
         <v>1</v>
       </c>
@@ -15067,11 +15088,11 @@
       <c r="D62" s="30">
         <v>2</v>
       </c>
-      <c r="E62" s="57" t="s">
+      <c r="E62" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F62" s="59"/>
-      <c r="G62" s="58"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="59"/>
       <c r="H62" s="30">
         <v>1</v>
       </c>
@@ -16306,18 +16327,18 @@
       <c r="A108" s="30">
         <v>4</v>
       </c>
-      <c r="B108" s="75" t="s">
+      <c r="B108" s="60" t="s">
         <v>237</v>
       </c>
-      <c r="C108" s="77"/>
+      <c r="C108" s="61"/>
       <c r="D108" s="30">
         <v>1</v>
       </c>
-      <c r="E108" s="75" t="s">
+      <c r="E108" s="60" t="s">
         <v>238</v>
       </c>
-      <c r="F108" s="76"/>
-      <c r="G108" s="77"/>
+      <c r="F108" s="62"/>
+      <c r="G108" s="61"/>
       <c r="H108" s="30">
         <v>1</v>
       </c>
@@ -16341,18 +16362,18 @@
       <c r="A109" s="30">
         <v>5</v>
       </c>
-      <c r="B109" s="57" t="s">
+      <c r="B109" s="58" t="s">
         <v>241</v>
       </c>
-      <c r="C109" s="58"/>
+      <c r="C109" s="59"/>
       <c r="D109" s="30">
         <v>1</v>
       </c>
-      <c r="E109" s="57" t="s">
+      <c r="E109" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F109" s="59"/>
-      <c r="G109" s="58"/>
+      <c r="F109" s="63"/>
+      <c r="G109" s="59"/>
       <c r="H109" s="30">
         <v>1</v>
       </c>
@@ -16374,12 +16395,12 @@
     </row>
     <row r="110" spans="1:19" ht="126">
       <c r="A110" s="30"/>
-      <c r="B110" s="57"/>
-      <c r="C110" s="58"/>
+      <c r="B110" s="58"/>
+      <c r="C110" s="59"/>
       <c r="D110" s="30"/>
-      <c r="E110" s="57"/>
-      <c r="F110" s="59"/>
-      <c r="G110" s="58"/>
+      <c r="E110" s="58"/>
+      <c r="F110" s="63"/>
+      <c r="G110" s="59"/>
       <c r="H110" s="30">
         <v>2</v>
       </c>
@@ -16404,9 +16425,9 @@
       <c r="B111" s="48"/>
       <c r="C111" s="49"/>
       <c r="D111" s="30"/>
-      <c r="E111" s="75"/>
-      <c r="F111" s="76"/>
-      <c r="G111" s="77"/>
+      <c r="E111" s="60"/>
+      <c r="F111" s="62"/>
+      <c r="G111" s="61"/>
       <c r="H111" s="30">
         <v>3</v>
       </c>
@@ -16568,11 +16589,11 @@
       <c r="D117" s="30">
         <v>2</v>
       </c>
-      <c r="E117" s="57" t="s">
+      <c r="E117" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F117" s="59"/>
-      <c r="G117" s="58"/>
+      <c r="F117" s="63"/>
+      <c r="G117" s="59"/>
       <c r="H117" s="30">
         <v>1</v>
       </c>
@@ -17810,11 +17831,11 @@
       <c r="D163" s="30">
         <v>3</v>
       </c>
-      <c r="E163" s="57" t="s">
+      <c r="E163" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="F163" s="59"/>
-      <c r="G163" s="58"/>
+      <c r="F163" s="63"/>
+      <c r="G163" s="59"/>
       <c r="H163" s="30"/>
       <c r="I163" s="51" t="s">
         <v>201</v>
@@ -17836,18 +17857,18 @@
       <c r="A164" s="30">
         <v>2</v>
       </c>
-      <c r="B164" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="C164" s="58"/>
+      <c r="B164" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="C164" s="59"/>
       <c r="D164" s="30">
         <v>1</v>
       </c>
-      <c r="E164" s="57" t="s">
+      <c r="E164" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F164" s="59"/>
-      <c r="G164" s="58"/>
+      <c r="F164" s="63"/>
+      <c r="G164" s="59"/>
       <c r="H164" s="30">
         <v>1</v>
       </c>
@@ -17874,11 +17895,11 @@
       <c r="D165" s="30">
         <v>2</v>
       </c>
-      <c r="E165" s="57" t="s">
+      <c r="E165" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F165" s="59"/>
-      <c r="G165" s="58"/>
+      <c r="F165" s="63"/>
+      <c r="G165" s="59"/>
       <c r="H165" s="30">
         <v>1</v>
       </c>
@@ -17886,7 +17907,7 @@
         <v>132</v>
       </c>
       <c r="J165" s="37" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K165" s="31"/>
       <c r="L165" s="32"/>
@@ -17913,7 +17934,7 @@
         <v>46</v>
       </c>
       <c r="J166" s="37" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K166" s="31"/>
       <c r="L166" s="32"/>
@@ -17940,7 +17961,7 @@
         <v>48</v>
       </c>
       <c r="J167" s="37" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K167" s="31"/>
       <c r="L167" s="32"/>
@@ -17967,7 +17988,7 @@
         <v>50</v>
       </c>
       <c r="J168" s="37" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K168" s="31"/>
       <c r="L168" s="32"/>
@@ -17994,7 +18015,7 @@
         <v>134</v>
       </c>
       <c r="J169" s="37" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K169" s="31"/>
       <c r="L169" s="32"/>
@@ -18129,7 +18150,7 @@
         <v>140</v>
       </c>
       <c r="J174" s="37" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K174" s="31"/>
       <c r="L174" s="32"/>
@@ -18156,7 +18177,7 @@
         <v>142</v>
       </c>
       <c r="J175" s="37" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K175" s="31"/>
       <c r="L175" s="32"/>
@@ -18183,7 +18204,7 @@
         <v>144</v>
       </c>
       <c r="J176" s="37" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K176" s="31"/>
       <c r="L176" s="32"/>
@@ -18210,7 +18231,7 @@
         <v>146</v>
       </c>
       <c r="J177" s="37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K177" s="31"/>
       <c r="L177" s="32"/>
@@ -18237,7 +18258,7 @@
         <v>148</v>
       </c>
       <c r="J178" s="37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K178" s="31"/>
       <c r="L178" s="32"/>
@@ -18264,7 +18285,7 @@
         <v>150</v>
       </c>
       <c r="J179" s="37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K179" s="31"/>
       <c r="L179" s="32"/>
@@ -18291,7 +18312,7 @@
         <v>152</v>
       </c>
       <c r="J180" s="37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K180" s="31"/>
       <c r="L180" s="32"/>
@@ -18318,7 +18339,7 @@
         <v>154</v>
       </c>
       <c r="J181" s="37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K181" s="31"/>
       <c r="L181" s="32"/>
@@ -18345,7 +18366,7 @@
         <v>156</v>
       </c>
       <c r="J182" s="37" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K182" s="31"/>
       <c r="L182" s="32"/>
@@ -18372,7 +18393,7 @@
         <v>146</v>
       </c>
       <c r="J183" s="37" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K183" s="31"/>
       <c r="L183" s="32"/>
@@ -18399,7 +18420,7 @@
         <v>159</v>
       </c>
       <c r="J184" s="37" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K184" s="31"/>
       <c r="L184" s="32"/>
@@ -18426,7 +18447,7 @@
         <v>161</v>
       </c>
       <c r="J185" s="37" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K185" s="31"/>
       <c r="L185" s="32"/>
@@ -18453,7 +18474,7 @@
         <v>163</v>
       </c>
       <c r="J186" s="37" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K186" s="31"/>
       <c r="L186" s="32"/>
@@ -18480,7 +18501,7 @@
         <v>156</v>
       </c>
       <c r="J187" s="37" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K187" s="31"/>
       <c r="L187" s="32"/>
@@ -18507,7 +18528,7 @@
         <v>166</v>
       </c>
       <c r="J188" s="37" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K188" s="31"/>
       <c r="L188" s="32"/>
@@ -18534,7 +18555,7 @@
         <v>168</v>
       </c>
       <c r="J189" s="37" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K189" s="31"/>
       <c r="L189" s="32"/>
@@ -18557,7 +18578,7 @@
       <c r="H190" s="30"/>
       <c r="I190" s="51"/>
       <c r="J190" s="37" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K190" s="31"/>
       <c r="L190" s="32"/>
@@ -18584,7 +18605,7 @@
         <v>171</v>
       </c>
       <c r="J191" s="37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K191" s="31"/>
       <c r="L191" s="32"/>
@@ -18611,7 +18632,7 @@
         <v>173</v>
       </c>
       <c r="J192" s="37" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K192" s="31"/>
       <c r="L192" s="32"/>
@@ -18638,7 +18659,7 @@
         <v>175</v>
       </c>
       <c r="J193" s="37" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K193" s="31"/>
       <c r="L193" s="32"/>
@@ -18665,7 +18686,7 @@
         <v>177</v>
       </c>
       <c r="J194" s="37" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K194" s="31"/>
       <c r="L194" s="32"/>
@@ -18692,7 +18713,7 @@
         <v>179</v>
       </c>
       <c r="J195" s="37" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K195" s="31"/>
       <c r="L195" s="32"/>
@@ -18719,7 +18740,7 @@
         <v>181</v>
       </c>
       <c r="J196" s="37" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K196" s="31"/>
       <c r="L196" s="32"/>
@@ -18746,7 +18767,7 @@
         <v>183</v>
       </c>
       <c r="J197" s="37" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K197" s="31"/>
       <c r="L197" s="32"/>
@@ -18773,7 +18794,7 @@
         <v>185</v>
       </c>
       <c r="J198" s="37" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K198" s="31"/>
       <c r="L198" s="32"/>
@@ -18800,7 +18821,7 @@
         <v>187</v>
       </c>
       <c r="J199" s="37" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K199" s="31"/>
       <c r="L199" s="32"/>
@@ -18827,7 +18848,7 @@
         <v>189</v>
       </c>
       <c r="J200" s="37" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K200" s="31"/>
       <c r="L200" s="32"/>
@@ -18854,7 +18875,7 @@
         <v>191</v>
       </c>
       <c r="J201" s="37" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K201" s="31"/>
       <c r="L201" s="32"/>
@@ -18881,7 +18902,7 @@
         <v>193</v>
       </c>
       <c r="J202" s="37" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K202" s="31"/>
       <c r="L202" s="32"/>
@@ -18908,7 +18929,7 @@
         <v>194</v>
       </c>
       <c r="J203" s="37" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K203" s="31"/>
       <c r="L203" s="32"/>
@@ -18935,7 +18956,7 @@
         <v>56</v>
       </c>
       <c r="J204" s="37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K204" s="31"/>
       <c r="L204" s="32"/>
@@ -18962,7 +18983,7 @@
         <v>58</v>
       </c>
       <c r="J205" s="37" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K205" s="31"/>
       <c r="L205" s="32"/>
@@ -18989,7 +19010,7 @@
         <v>60</v>
       </c>
       <c r="J206" s="37" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K206" s="31"/>
       <c r="L206" s="32"/>
@@ -19016,7 +19037,7 @@
         <v>62</v>
       </c>
       <c r="J207" s="37" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K207" s="31"/>
       <c r="L207" s="32"/>
@@ -19043,7 +19064,7 @@
         <v>64</v>
       </c>
       <c r="J208" s="37" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K208" s="31"/>
       <c r="L208" s="32"/>
@@ -19070,7 +19091,7 @@
         <v>66</v>
       </c>
       <c r="J209" s="37" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K209" s="31"/>
       <c r="L209" s="32"/>
@@ -19097,7 +19118,7 @@
         <v>68</v>
       </c>
       <c r="J210" s="37" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K210" s="31"/>
       <c r="L210" s="32"/>
@@ -19111,12 +19132,12 @@
     </row>
     <row r="211" spans="1:19" ht="31.5" customHeight="1">
       <c r="A211" s="38"/>
-      <c r="B211" s="78"/>
-      <c r="C211" s="79"/>
+      <c r="B211" s="55"/>
+      <c r="C211" s="56"/>
       <c r="D211" s="38"/>
-      <c r="E211" s="78"/>
-      <c r="F211" s="80"/>
-      <c r="G211" s="79"/>
+      <c r="E211" s="55"/>
+      <c r="F211" s="57"/>
+      <c r="G211" s="56"/>
       <c r="H211" s="38"/>
       <c r="I211" s="46"/>
       <c r="J211" s="39"/>
@@ -19163,28 +19184,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B211:C211"/>
-    <mergeCell ref="E211:G211"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E164:G164"/>
-    <mergeCell ref="E165:G165"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E111:G111"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="E163:G163"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="E60:G60"/>
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E6:G6"/>
@@ -19201,6 +19200,28 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="B211:C211"/>
+    <mergeCell ref="E211:G211"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E164:G164"/>
+    <mergeCell ref="E165:G165"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E111:G111"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="E163:G163"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
@@ -19225,14 +19246,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8caee9ae-ac4c-4a91-bf2f-c539f84f9d4e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="991e4cd9-443b-4484-87b4-0c84d1f9a0ac">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19431,16 +19450,18 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8caee9ae-ac4c-4a91-bf2f-c539f84f9d4e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="991e4cd9-443b-4484-87b4-0c84d1f9a0ac">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF1E623F-B127-4777-BA82-6CF058B03372}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DFE76D1-1C80-4DBB-B5E5-1A118C3732F7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19448,5 +19469,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DFE76D1-1C80-4DBB-B5E5-1A118C3732F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF1E623F-B127-4777-BA82-6CF058B03372}"/>
 </file>